--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/INDIANA_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/INDIANA_2018.xlsx
@@ -5028,7 +5028,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C260">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C638">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C724">
@@ -13398,7 +13398,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C725">
@@ -13992,7 +13992,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C758">
